--- a/sources/ETERNUM.xlsx
+++ b/sources/ETERNUM.xlsx
@@ -2590,7 +2590,11 @@
           <t>https://yourroyalhouse.ge/en/shop/eternum/arcade/arcade-table-fork/</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://yourroyalhouse.ge/wp-content/uploads/2019/05/1620-1-copy.jpg</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>https://yourroyalhouse.ge/en/shop/eternum/arcade/arcade-table-fork/</t>
@@ -3248,7 +3252,11 @@
           <t>https://yourroyalhouse.ge/en/shop/eternum/arcade/arcade-table-knife-mono/</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://yourroyalhouse.ge/wp-content/uploads/2019/05/1620-5-copy-scaled.jpg</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>https://yourroyalhouse.ge/en/shop/eternum/arcade/arcade-table-knife-mono/</t>
@@ -3392,7 +3400,11 @@
           <t>https://yourroyalhouse.ge/en/shop/eternum/arcade/arcade-dessert-knife-hh/</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://yourroyalhouse.ge/wp-content/uploads/2019/05/1620-61-copy-scaled.jpg</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>https://yourroyalhouse.ge/en/shop/eternum/arcade/arcade-dessert-knife-hh/</t>
@@ -7019,7 +7031,11 @@
           <t>https://yourroyalhouse.ge/en/shop/eternum/anzo-table-fork/</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://yourroyalhouse.ge/wp-content/uploads/2019/05/1820-1-copy-scaled.jpg</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr">
         <is>
           <t>https://yourroyalhouse.ge/en/shop/eternum/anzo-table-fork/</t>
@@ -7528,7 +7544,11 @@
           <t>https://yourroyalhouse.ge/en/shop/eternum/anzo-table-spoon/</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://yourroyalhouse.ge/wp-content/uploads/2019/05/1820-15-copy.jpg</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr">
         <is>
           <t>https://yourroyalhouse.ge/en/shop/eternum/anzo-table-spoon/</t>
@@ -12744,7 +12764,11 @@
           <t>https://yourroyalhouse.ge/en/shop/eternum/alaska/alaska-table-spoon/</t>
         </is>
       </c>
-      <c r="J292" t="inlineStr"/>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>https://yourroyalhouse.ge/wp-content/uploads/2019/05/2080-2-copy.jpg</t>
+        </is>
+      </c>
       <c r="K292" t="inlineStr">
         <is>
           <t>https://yourroyalhouse.ge/en/shop/eternum/alaska/alaska-table-spoon/</t>
@@ -12801,7 +12825,11 @@
           <t>https://yourroyalhouse.ge/en/shop/eternum/alaska/alaska-cocktail-spoon/</t>
         </is>
       </c>
-      <c r="J293" t="inlineStr"/>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>https://yourroyalhouse.ge/wp-content/uploads/2019/05/2080-25-copy.jpg</t>
+        </is>
+      </c>
       <c r="K293" t="inlineStr">
         <is>
           <t>https://yourroyalhouse.ge/en/shop/eternum/alaska/alaska-cocktail-spoon/</t>
@@ -13346,7 +13374,11 @@
           <t>https://yourroyalhouse.ge/en/shop/eternum/alaska/alaska-table-knife-mono/</t>
         </is>
       </c>
-      <c r="J302" t="inlineStr"/>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>https://yourroyalhouse.ge/wp-content/uploads/2019/05/2080-5-copy.jpg</t>
+        </is>
+      </c>
       <c r="K302" t="inlineStr">
         <is>
           <t>https://yourroyalhouse.ge/en/shop/eternum/alaska/alaska-table-knife-mono/</t>
@@ -13403,7 +13435,11 @@
           <t>https://yourroyalhouse.ge/en/shop/eternum/alaska/alaska-dessert-knife/</t>
         </is>
       </c>
-      <c r="J303" t="inlineStr"/>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>https://yourroyalhouse.ge/wp-content/uploads/2019/05/2080-6-copy-scaled.jpg</t>
+        </is>
+      </c>
       <c r="K303" t="inlineStr">
         <is>
           <t>https://yourroyalhouse.ge/en/shop/eternum/alaska/alaska-dessert-knife/</t>
